--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486797_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486797_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4152</v>
+        <v>2.4884</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5152</v>
+        <v>2.0603</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>0.4282</v>
       </c>
       <c r="G2" t="n">
         <v>2.7392</v>
@@ -610,13 +610,13 @@
         <v>0.7723</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5062</v>
+        <v>0.5794</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5512</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.955</v>
+        <v>0.4832</v>
       </c>
       <c r="V2" t="n">
         <v>0.3282</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.8686</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.7453</v>
+        <v>-2.5866</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3062</v>
+        <v>3.4552</v>
       </c>
       <c r="G3" t="n">
         <v>1.3982</v>
@@ -688,13 +688,13 @@
         <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5903</v>
+        <v>-0.2827</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4142</v>
+        <v>-0.2556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1761</v>
+        <v>-0.0271</v>
       </c>
       <c r="V3" t="n">
         <v>1.6838</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1075</v>
+        <v>0.0415</v>
       </c>
       <c r="E4" t="n">
         <v>-0.3387</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2312</v>
+        <v>0.3802</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2288</v>
@@ -766,13 +766,13 @@
         <v>0.3862</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9212</v>
+        <v>-0.7723</v>
       </c>
       <c r="T4" t="n">
         <v>-0.4415</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4798</v>
+        <v>-0.3308</v>
       </c>
       <c r="V4" t="n">
         <v>0.6565</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1835</v>
+        <v>-0.1587</v>
       </c>
       <c r="E5" t="n">
         <v>0.0207</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2042</v>
+        <v>-0.1794</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1174</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5816</v>
+        <v>-0.3526</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3046</v>
+        <v>-1.2494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.723</v>
+        <v>0.8968</v>
       </c>
       <c r="G6" t="n">
         <v>0.0668</v>
@@ -922,13 +922,13 @@
         <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4634</v>
+        <v>-0.2343</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4693</v>
+        <v>-0.4142</v>
       </c>
       <c r="U6" t="n">
-        <v>0.006</v>
+        <v>0.1798</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5712</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9703</v>
+        <v>-1.723</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8998</v>
+        <v>-1.0297</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9295</v>
+        <v>-0.6933</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.328</v>
+        <v>-2.3331</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.738</v>
+        <v>-0.242</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.59</v>
+        <v>-2.0911</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3967</v>
+        <v>-1.1941</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6688</v>
+        <v>0.1035</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7279</v>
+        <v>-1.2976</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0687</v>
+        <v>-1.139</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0692</v>
+        <v>-0.3454</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1379</v>
+        <v>-0.7935</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5446</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3255</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>-0.6691</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2815</v>
+        <v>-0.041</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2277</v>
+        <v>1.7989</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0578</v>
+        <v>-1.9414</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.526</v>
+        <v>-2.7964</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5318000000000001</v>
+        <v>0.855</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1161</v>
+        <v>-1.328</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6617</v>
+        <v>-0.738</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4544</v>
+        <v>-0.59</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7028</v>
+        <v>-1.3967</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6622</v>
+        <v>-0.6688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0407</v>
+        <v>-0.7279</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4132</v>
+        <v>0.0687</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0005</v>
+        <v>-0.0692</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4137</v>
+        <v>0.1379</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R8" t="n">
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3749</v>
+        <v>-0.2965</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2321</v>
+        <v>0.2071</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4128</v>
+        <v>1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>J. RODRÍGUEZ MORANTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1106</v>
+        <v>-2.1072</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2435</v>
+        <v>-3.5529</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8671</v>
+        <v>1.4457</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3331</v>
+        <v>-1.5749</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.242</v>
+        <v>-1.4483</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0911</v>
+        <v>-0.1266</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1941</v>
+        <v>0.0333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1035</v>
+        <v>-1.0338</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2976</v>
+        <v>1.0671</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.139</v>
+        <v>-1.6082</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3454</v>
+        <v>-0.4145</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7935</v>
+        <v>-1.1937</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0978</v>
+        <v>-0.5517</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8829</v>
+        <v>-0.6901</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2149</v>
+        <v>0.1384</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5133</v>
+        <v>0.9847</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7989</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRÍGUEZ MORANTE</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4714</v>
+        <v>-2.1241</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7185</v>
+        <v>-1.3192</v>
       </c>
       <c r="F10" t="n">
-        <v>1.247</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5749</v>
+        <v>1.1161</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4483</v>
+        <v>0.6617</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1266</v>
+        <v>0.4544</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0333</v>
+        <v>0.7028</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0338</v>
+        <v>0.6622</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0671</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6082</v>
+        <v>0.4132</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4145</v>
+        <v>-0.0005</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1937</v>
+        <v>0.4137</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.8962</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.9308</v>
+        <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9159</v>
+        <v>-0.4412</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8556</v>
+        <v>-0.4002</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0603</v>
+        <v>-0.0411</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9847</v>
+        <v>-2.4128</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9847</v>
+        <v>-1.7563</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2747</v>
+        <v>-4.1836</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5491</v>
+        <v>-4.3836</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2744</v>
+        <v>0.1999</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9153</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0425</v>
+        <v>-0.9514</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0212</v>
+        <v>-0.8556</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0213</v>
+        <v>-0.0958</v>
       </c>
       <c r="V11" t="n">
         <v>1.8415</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7451</v>
+        <v>-4.5065</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6016</v>
+        <v>-3.3878</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1435</v>
+        <v>-1.1186</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7893</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.535</v>
+        <v>-0.2964</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.697</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3758</v>
+        <v>0.4006</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.5263</v>
+        <v>-13.6986</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.3912</v>
+        <v>-18.5633</v>
       </c>
       <c r="F13" t="n">
-        <v>4.864699999999999</v>
+        <v>4.864800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.966500000000001</v>
+        <v>-6.9665</v>
       </c>
       <c r="H13" t="n">
         <v>-2.7619</v>
@@ -1453,7 +1453,7 @@
         <v>-5.6312</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.7996</v>
+        <v>-3.799600000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-1.8316</v>
@@ -1468,16 +1468,16 @@
         <v>12.5501</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8265</v>
+        <v>-3.9986</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.658300000000001</v>
+        <v>-4.8307</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8317999999999999</v>
+        <v>0.8320000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>4.023999999999999</v>
+        <v>4.024000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>6.9101</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5065</v>
+        <v>3.4826</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0113</v>
+        <v>-1.2651</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4952</v>
+        <v>4.7478</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9942</v>
+        <v>4.4785</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0615</v>
+        <v>2.0618</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0556</v>
+        <v>2.4167</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0163</v>
+        <v>2.2452</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2838</v>
+        <v>1.0967</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7325</v>
+        <v>1.1485</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0221</v>
+        <v>2.2332</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3453</v>
+        <v>0.9651</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3232</v>
+        <v>1.2681</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3169</v>
+        <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5743</v>
+        <v>0.4483</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0883</v>
+        <v>-0.6142</v>
       </c>
       <c r="U14" t="n">
-        <v>0.486</v>
+        <v>1.0624</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4135</v>
+        <v>-0.2856</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1279</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2856</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3041</v>
+        <v>3.4629</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0779</v>
+        <v>0.9429</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2262</v>
+        <v>2.52</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0868</v>
+        <v>0.9942</v>
       </c>
       <c r="H15" t="n">
-        <v>2.27</v>
+        <v>-0.0615</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1832</v>
+        <v>1.0556</v>
       </c>
       <c r="J15" t="n">
-        <v>3.212</v>
+        <v>1.0163</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4772</v>
+        <v>0.2838</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7347</v>
+        <v>0.7325</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1251</v>
+        <v>-0.0221</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2072</v>
+        <v>-0.3453</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9179</v>
+        <v>0.3232</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7031</v>
+        <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7153</v>
+        <v>1.5307</v>
       </c>
       <c r="T15" t="n">
-        <v>0.882</v>
+        <v>1.0199</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8334</v>
+        <v>0.5108</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2703</v>
+        <v>-0.4135</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0852</v>
+        <v>-0.1279</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1851</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6427</v>
+        <v>2.5318</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7822</v>
+        <v>1.8916</v>
       </c>
       <c r="F16" t="n">
-        <v>4.425</v>
+        <v>0.6402</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4785</v>
+        <v>1.9817</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0618</v>
+        <v>0.7587</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4167</v>
+        <v>1.2231</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2452</v>
+        <v>1.9482</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0967</v>
+        <v>0.759</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1485</v>
+        <v>1.1892</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2332</v>
+        <v>0.0335</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9651</v>
+        <v>-0.0003</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2681</v>
+        <v>0.0338</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7377</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3917</v>
+        <v>0.4688</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1313</v>
+        <v>-0.2763</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7396</v>
+        <v>0.7451</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2856</v>
+        <v>-1.2703</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4821</v>
+        <v>2.5057</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8916</v>
+        <v>1.3539</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5905</v>
+        <v>1.1518</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9817</v>
+        <v>2.0868</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7587</v>
+        <v>2.27</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2231</v>
+        <v>-0.1832</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9482</v>
+        <v>3.212</v>
       </c>
       <c r="K17" t="n">
-        <v>0.759</v>
+        <v>2.4772</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1892</v>
+        <v>0.7347</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0335</v>
+        <v>-1.1251</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0003</v>
+        <v>-0.2072</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0338</v>
+        <v>-0.9179</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3169</v>
+        <v>2.7031</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4191</v>
+        <v>0.9169</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2763</v>
+        <v>0.158</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6954</v>
+        <v>0.7589</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2703</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1851</v>
+        <v>-0.0852</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4554</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2467</v>
+        <v>2.379</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.555</v>
+        <v>-0.3481</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8017</v>
+        <v>2.7272</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4992</v>
@@ -1858,13 +1858,13 @@
         <v>2.51</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3364</v>
+        <v>0.4687</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5522</v>
+        <v>-0.3453</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8141</v>
       </c>
       <c r="V18" t="n">
         <v>0.8995</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8946</v>
+        <v>0.9277</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7546</v>
+        <v>-1.5477</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6492</v>
+        <v>2.4754</v>
       </c>
       <c r="G19" t="n">
         <v>3.2334</v>
@@ -1936,13 +1936,13 @@
         <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1326</v>
+        <v>0.1656</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4966</v>
+        <v>-0.2898</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6293</v>
+        <v>0.4554</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3129</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7464</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.197</v>
+        <v>-2.7833</v>
       </c>
       <c r="F20" t="n">
-        <v>3.9434</v>
+        <v>3.6951</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7298</v>
@@ -2014,13 +2014,13 @@
         <v>3.4754</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2759</v>
+        <v>0.4413</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.4144</v>
       </c>
       <c r="U20" t="n">
-        <v>1.104</v>
+        <v>0.8557</v>
       </c>
       <c r="V20" t="n">
         <v>2.6557</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6135</v>
+        <v>-0.3517</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6123</v>
+        <v>-0.4747</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0012</v>
+        <v>0.123</v>
       </c>
       <c r="G21" t="n">
         <v>0.0145</v>
@@ -2092,13 +2092,13 @@
         <v>2.51</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7171999999999999</v>
+        <v>0.5446</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.365</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0555</v>
+        <v>0.1796</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4554</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6834</v>
+        <v>-1.3234</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9445</v>
+        <v>-2.6343</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2611</v>
+        <v>1.3108</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5937</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5185</v>
+        <v>-0.1585</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.745</v>
+        <v>-0.4348</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2265</v>
+        <v>0.2762</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5712</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.5262</v>
+        <v>14.5264</v>
       </c>
       <c r="E23" t="n">
         <v>-4.864800000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>19.3911</v>
+        <v>19.3913</v>
       </c>
       <c r="G23" t="n">
         <v>6.9664</v>
@@ -2221,7 +2221,7 @@
         <v>4.204400000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>5.631300000000001</v>
+        <v>5.6313</v>
       </c>
       <c r="K23" t="n">
         <v>3.7995</v>
@@ -2248,13 +2248,13 @@
         <v>19.3077</v>
       </c>
       <c r="S23" t="n">
-        <v>4.8262</v>
+        <v>4.8264</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8319</v>
+        <v>-0.8318999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>5.658300000000001</v>
+        <v>5.6582</v>
       </c>
       <c r="V23" t="n">
         <v>-4.024</v>
